--- a/july 2026/GT_JULY_26/02-07-2026/Furqan.xlsx
+++ b/july 2026/GT_JULY_26/02-07-2026/Furqan.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24ADBCCB-222B-4784-8B45-94D2B1F05942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB4B4F5-C7A6-4AE0-82F0-8A064414044E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -3295,7 +3295,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -3323,7 +3323,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -3626,8 +3626,8 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
-        <v>0</v>
+        <f>I16*3.5%</f>
+        <v>36.723750000000003</v>
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
@@ -3635,19 +3635,19 @@
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>965.31</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>212.3682</v>
+        <v>204.28897500000002</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>29.441954999999997</v>
+        <v>28.321880625000002</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>1207.1201549999998</v>
+        <v>1161.1971056249999</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -3687,9 +3687,9 @@
         <v>1049.25</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
-        <v>0</v>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
+        <v>36.723750000000003</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
@@ -3697,19 +3697,19 @@
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>965.31</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>212.3682</v>
+        <v>204.28897500000002</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>29.441954999999997</v>
+        <v>28.321880625000002</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>1207.1201549999998</v>
+        <v>1161.1971056249999</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3861,9 +3861,9 @@
         <v>1452.8</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
@@ -3871,19 +3871,19 @@
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>1336.576</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>294.04671999999999</v>
+        <v>282.86016000000001</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>40.765568000000002</v>
+        <v>39.214704000000005</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>1671.3882880000001</v>
+        <v>1607.802864</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -3919,9 +3919,9 @@
         <v>1452.8</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
@@ -3929,19 +3929,19 @@
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>1336.576</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>294.04671999999999</v>
+        <v>282.86016000000001</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>40.765568000000002</v>
+        <v>39.214704000000005</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>1671.3882880000001</v>
+        <v>1607.802864</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -3975,12 +3975,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -4136,7 +4136,7 @@
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>175.14350000000002</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
@@ -4144,19 +4144,19 @@
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>4603.7719999999999</v>
+        <v>4428.6285000000007</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>1012.8298400000001</v>
+        <v>974.29827</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>140.41504599999999</v>
+        <v>135.07316925000001</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>5757.0168859999994</v>
+        <v>5537.9999392500004</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -4248,7 +4248,7 @@
       <c r="O30" s="250"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>0</v>
+        <v>175.14350000000002</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4270,7 +4270,7 @@
       <c r="O31" s="250"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>4603.7720000000008</v>
+        <v>4428.6285000000007</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>1012.8298400000001</v>
+        <v>974.29827</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -4317,7 +4317,7 @@
       <c r="O33" s="252"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>5616.6018400000012</v>
+        <v>5402.9267700000009</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>140.41504600000005</v>
+        <v>135.07316925000003</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -4352,7 +4352,7 @@
       <c r="O35" s="230"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>5757.0168860000013</v>
+        <v>5537.9999392500013</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4524,7 +4524,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -4552,7 +4552,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -4912,8 +4912,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -4972,7 +4972,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5030,9 +5030,9 @@
         <v>871.68000000000006</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30.508800000000004</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
@@ -5040,19 +5040,19 @@
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>801.94560000000001</v>
+        <v>771.43680000000006</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>176.428032</v>
+        <v>169.71609600000002</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>24.459340800000003</v>
+        <v>23.528822400000003</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>1002.8329728</v>
+        <v>964.68171840000002</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5088,9 +5088,9 @@
         <v>871.68000000000006</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30.508800000000004</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
@@ -5098,19 +5098,19 @@
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>801.94560000000001</v>
+        <v>771.43680000000006</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>176.428032</v>
+        <v>169.71609600000002</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>24.459340800000003</v>
+        <v>23.528822400000003</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>1002.8329728</v>
+        <v>964.68171840000002</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5146,9 +5146,9 @@
         <v>871.68000000000006</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30.508800000000004</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
@@ -5156,19 +5156,19 @@
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>801.94560000000001</v>
+        <v>771.43680000000006</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>176.428032</v>
+        <v>169.71609600000002</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>24.459340800000003</v>
+        <v>23.528822400000003</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>1002.8329728</v>
+        <v>964.68171840000002</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5202,12 +5202,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -5363,7 +5363,7 @@
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>91.52640000000001</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
@@ -5371,19 +5371,19 @@
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>2405.8368</v>
+        <v>2314.3104000000003</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>529.28409599999998</v>
+        <v>509.14828800000009</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>73.378022400000006</v>
+        <v>70.586467200000016</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>3008.4989184000001</v>
+        <v>2894.0451552</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5475,7 +5475,7 @@
       <c r="O30" s="250"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>0</v>
+        <v>91.52640000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5497,7 +5497,7 @@
       <c r="O31" s="250"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>2405.8368</v>
+        <v>2314.3103999999998</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>529.28409599999998</v>
+        <v>509.14828800000009</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5544,7 +5544,7 @@
       <c r="O33" s="252"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>2935.1208959999999</v>
+        <v>2823.4586879999997</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>73.378022400000006</v>
+        <v>70.586467200000001</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5579,7 +5579,7 @@
       <c r="O35" s="230"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>3008.4989184000001</v>
+        <v>2894.0451551999995</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5751,7 +5751,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -5779,7 +5779,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -6082,8 +6082,8 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
-        <v>0</v>
+        <f>I16*3.5%</f>
+        <v>36.723750000000003</v>
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
@@ -6091,19 +6091,19 @@
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>965.31</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>212.3682</v>
+        <v>204.28897500000002</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>5.8883909999999995</v>
+        <v>5.6643761250000004</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>1183.5665909999998</v>
+        <v>1138.539601125</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -6143,9 +6143,9 @@
         <v>1049.25</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
-        <v>0</v>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
+        <v>36.723750000000003</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
@@ -6153,19 +6153,19 @@
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>965.31</v>
+        <v>928.58625000000006</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>212.3682</v>
+        <v>204.28897500000002</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>5.8883909999999995</v>
+        <v>5.6643761250000004</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>1183.5665909999998</v>
+        <v>1138.539601125</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -6203,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6427,12 +6427,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -6588,7 +6588,7 @@
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>73.447500000000005</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
@@ -6596,19 +6596,19 @@
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1930.62</v>
+        <v>1857.1725000000001</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>424.7364</v>
+        <v>408.57795000000004</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>11.776781999999999</v>
+        <v>11.328752250000001</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>2367.1331819999996</v>
+        <v>2277.07920225</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -6700,7 +6700,7 @@
       <c r="O30" s="250"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>0</v>
+        <v>73.447500000000005</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6722,7 +6722,7 @@
       <c r="O31" s="250"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1930.62</v>
+        <v>1857.1724999999999</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>424.7364</v>
+        <v>408.57795000000004</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6769,7 +6769,7 @@
       <c r="O33" s="252"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>2355.3563999999997</v>
+        <v>2265.75045</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>11.776781999999999</v>
+        <v>11.328752250000001</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6804,7 +6804,7 @@
       <c r="O35" s="230"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>2367.1331819999996</v>
+        <v>2277.07920225</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6976,7 +6976,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -7004,7 +7004,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -7364,8 +7364,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -7424,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7650,29 +7650,29 @@
         <v>470.76000000000005</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>16.476600000000005</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>23.538000000000004</v>
+        <f>I22*10%</f>
+        <v>47.076000000000008</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>430.74540000000002</v>
+        <v>407.20740000000001</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>94.763987999999998</v>
+        <v>89.585628</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>13.137734700000003</v>
+        <v>12.419825700000001</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>538.64712270000007</v>
+        <v>509.21285369999998</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -7815,23 +7815,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>23.538000000000004</v>
+        <v>47.076000000000008</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>430.74540000000002</v>
+        <v>407.20740000000001</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>94.763987999999998</v>
+        <v>89.585628</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>13.137734700000003</v>
+        <v>12.419825700000001</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>538.64712270000007</v>
+        <v>509.21285369999998</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -7902,7 +7902,7 @@
       <c r="O29" s="250"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>23.538000000000004</v>
+        <v>47.076000000000008</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7945,7 +7945,7 @@
       <c r="O31" s="250"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>430.74540000000002</v>
+        <v>407.20740000000001</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>94.763987999999998</v>
+        <v>89.585628</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -7992,7 +7992,7 @@
       <c r="O33" s="252"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>525.50938800000006</v>
+        <v>496.79302799999999</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>13.137734700000003</v>
+        <v>12.419825700000001</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -8027,7 +8027,7 @@
       <c r="O35" s="230"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>538.64712270000007</v>
+        <v>509.21285369999998</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -8199,7 +8199,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -8227,7 +8227,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -8587,8 +8587,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -8647,7 +8647,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8703,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -8761,9 +8761,9 @@
         <v>1452.8</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
@@ -8771,19 +8771,19 @@
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>1336.576</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>294.04671999999999</v>
+        <v>282.86016000000001</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>8.1531136000000011</v>
+        <v>7.8429408</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>1638.7758336000002</v>
+        <v>1576.4311008</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -8819,9 +8819,9 @@
         <v>1452.8</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
@@ -8829,19 +8829,19 @@
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>1336.576</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>294.04671999999999</v>
+        <v>282.86016000000001</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>8.1531136000000011</v>
+        <v>7.8429408</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>1638.7758336000002</v>
+        <v>1576.4311008</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -8875,12 +8875,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -9036,7 +9036,7 @@
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
@@ -9044,19 +9044,19 @@
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>2673.152</v>
+        <v>2571.4560000000001</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>588.09343999999999</v>
+        <v>565.72032000000002</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>16.306227200000002</v>
+        <v>15.6858816</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>3277.5516672000003</v>
+        <v>3152.8622015999999</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -9148,7 +9148,7 @@
       <c r="O30" s="250"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9170,7 +9170,7 @@
       <c r="O31" s="250"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>2673.152</v>
+        <v>2571.4560000000001</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9195,7 +9195,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>588.09343999999999</v>
+        <v>565.72032000000002</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -9217,7 +9217,7 @@
       <c r="O33" s="252"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>3261.2454400000001</v>
+        <v>3137.17632</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>16.306227200000002</v>
+        <v>15.6858816</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -9252,7 +9252,7 @@
       <c r="O35" s="230"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>3277.5516672000003</v>
+        <v>3152.8622015999999</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -9424,7 +9424,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -9452,7 +9452,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -9812,8 +9812,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -9872,7 +9872,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -9930,9 +9930,9 @@
         <v>1452.8</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
@@ -9940,19 +9940,19 @@
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>1336.576</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>294.04671999999999</v>
+        <v>282.86016000000001</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>40.765568000000002</v>
+        <v>39.214704000000005</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>1671.3882880000001</v>
+        <v>1607.802864</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -9988,9 +9988,9 @@
         <v>1452.8</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
@@ -9998,19 +9998,19 @@
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>1336.576</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>294.04671999999999</v>
+        <v>282.86016000000001</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>40.765568000000002</v>
+        <v>39.214704000000005</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>1671.3882880000001</v>
+        <v>1607.802864</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -10046,9 +10046,9 @@
         <v>1452.8</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>50.848000000000006</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
@@ -10056,19 +10056,19 @@
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>1336.576</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>294.04671999999999</v>
+        <v>282.86016000000001</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>40.765568000000002</v>
+        <v>39.214704000000005</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>1671.3882880000001</v>
+        <v>1607.802864</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -10102,12 +10102,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -10263,7 +10263,7 @@
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>152.54400000000001</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
@@ -10271,19 +10271,19 @@
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>4009.7280000000001</v>
+        <v>3857.1840000000002</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>882.14015999999992</v>
+        <v>848.58048000000008</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>122.29670400000001</v>
+        <v>117.64411200000001</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>5014.1648640000003</v>
+        <v>4823.4085919999998</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -10375,7 +10375,7 @@
       <c r="O30" s="250"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>0</v>
+        <v>152.54400000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10397,7 +10397,7 @@
       <c r="O31" s="250"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>4009.7279999999996</v>
+        <v>3857.1839999999997</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>882.14015999999992</v>
+        <v>848.58048000000008</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -10444,7 +10444,7 @@
       <c r="O33" s="252"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>4891.86816</v>
+        <v>4705.7644799999998</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -10469,7 +10469,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>122.29670400000001</v>
+        <v>117.64411200000001</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -10479,7 +10479,7 @@
       <c r="O35" s="230"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>5014.1648640000003</v>
+        <v>4823.4085919999998</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -10648,7 +10648,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -10676,7 +10676,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -11036,8 +11036,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -11096,7 +11096,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11152,7 +11152,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11208,7 +11208,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11264,7 +11264,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -11322,29 +11322,29 @@
         <v>941.5200000000001</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>32.95320000000001</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>47.076000000000008</v>
+        <f>I22*10%</f>
+        <v>94.152000000000015</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>861.49080000000004</v>
+        <v>814.41480000000001</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>155.068344</v>
+        <v>146.59466399999999</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>25.413978600000004</v>
+        <v>24.025236599999999</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1041.9731226000001</v>
+        <v>985.03470059999995</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -11487,23 +11487,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>47.076000000000008</v>
+        <v>94.152000000000015</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>861.49080000000004</v>
+        <v>814.41480000000001</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>155.068344</v>
+        <v>146.59466399999999</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>25.413978600000004</v>
+        <v>24.025236599999999</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1041.9731226000001</v>
+        <v>985.03470059999995</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -11574,7 +11574,7 @@
       <c r="O29" s="250"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>47.076000000000008</v>
+        <v>94.152000000000015</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11617,7 +11617,7 @@
       <c r="O31" s="250"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>861.49080000000004</v>
+        <v>814.41480000000001</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>155.068344</v>
+        <v>146.59466399999999</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -11664,7 +11664,7 @@
       <c r="O33" s="252"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1016.5591440000001</v>
+        <v>961.00946399999998</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>25.413978600000004</v>
+        <v>24.025236599999999</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -11699,7 +11699,7 @@
       <c r="O35" s="230"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1041.9731226000001</v>
+        <v>985.03470059999995</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -11867,7 +11867,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -11895,7 +11895,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -12255,8 +12255,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -12315,7 +12315,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -12371,7 +12371,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -12427,7 +12427,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -12483,7 +12483,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -12539,12 +12539,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -13084,7 +13084,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -13112,7 +13112,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -13472,8 +13472,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -13532,7 +13532,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13588,7 +13588,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13700,7 +13700,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -13756,12 +13756,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -14301,7 +14301,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -14329,7 +14329,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -14689,8 +14689,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -14749,7 +14749,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -14805,7 +14805,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -14861,7 +14861,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -14917,7 +14917,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -14973,12 +14973,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -18268,7 +18268,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -18296,7 +18296,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -18597,7 +18597,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -18656,8 +18656,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -18716,7 +18716,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -18772,7 +18772,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -18828,7 +18828,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -18884,7 +18884,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -18940,12 +18940,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -19485,7 +19485,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -19513,7 +19513,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -19873,8 +19873,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -19933,7 +19933,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -19989,7 +19989,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -20101,7 +20101,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -20157,12 +20157,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -20702,7 +20702,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -20730,7 +20730,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -21031,7 +21031,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -21090,8 +21090,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -21150,7 +21150,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21206,7 +21206,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21262,7 +21262,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21318,7 +21318,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -21374,12 +21374,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -21919,7 +21919,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -21947,7 +21947,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -22248,7 +22248,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -22307,8 +22307,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -22367,7 +22367,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -22423,7 +22423,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -22479,7 +22479,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -22535,7 +22535,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -22591,12 +22591,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -23141,7 +23141,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -23169,7 +23169,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -23433,7 +23433,7 @@
       </c>
       <c r="U15" s="164">
         <f>+'2'!P35</f>
-        <v>1585.0454784000003</v>
+        <v>1524.7448352000001</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -23478,7 +23478,7 @@
       </c>
       <c r="K16" s="172">
         <f>+'1'!K16+'2'!K16+'4'!K16+'3'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16</f>
-        <v>0</v>
+        <v>84.464625000000012</v>
       </c>
       <c r="L16" s="175">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
@@ -23486,19 +23486,19 @@
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>2220.2130000000002</v>
+        <v>2135.7483750000001</v>
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>488.44686000000002</v>
+        <v>469.86464250000006</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>37.096863299999995</v>
+        <v>35.685569587499998</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>2745.7567233</v>
+        <v>2641.2985870875004</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23507,7 +23507,7 @@
       </c>
       <c r="U16" s="164">
         <f>+'3'!P35</f>
-        <v>1490.9397644999999</v>
+        <v>1425.5701598999999</v>
       </c>
       <c r="XFD16" t="s">
         <v>82</v>
@@ -23552,7 +23552,7 @@
       </c>
       <c r="K17" s="172">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
-        <v>0</v>
+        <v>168.92925</v>
       </c>
       <c r="L17" s="175">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
@@ -23560,19 +23560,19 @@
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>4440.4260000000004</v>
+        <v>4271.4967500000002</v>
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>976.89372000000003</v>
+        <v>939.72928500000012</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>50.640162599999996</v>
+        <v>48.713634675000009</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>5467.9598826000001</v>
+        <v>5259.9396696750009</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23581,7 +23581,7 @@
       </c>
       <c r="U17" s="164">
         <f>+'4'!P35</f>
-        <v>2367.1331819999996</v>
+        <v>2277.07920225</v>
       </c>
       <c r="XFD17" t="s">
         <v>83</v>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="U18" s="164">
         <f>+'5'!P35</f>
-        <v>1616.5886720000003</v>
+        <v>1555.0880160000002</v>
       </c>
     </row>
     <row r="19" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23696,7 +23696,7 @@
       </c>
       <c r="K19" s="172">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
-        <v>30.508800000000004</v>
+        <v>106.78080000000001</v>
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
@@ -23704,19 +23704,19 @@
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>4229.1008000000011</v>
+        <v>4152.8288000000002</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>539.83142399999997</v>
+        <v>524.57702400000005</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>48.765411200000003</v>
+        <v>47.083359360000003</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>4817.6976352000011</v>
+        <v>4724.4891833600004</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="U19" s="164">
         <f>+'6'!P35</f>
-        <v>3049.9930246500003</v>
+        <v>2929.5767934224996</v>
       </c>
     </row>
     <row r="20" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="K20" s="172">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
-        <v>0</v>
+        <v>137.28960000000001</v>
       </c>
       <c r="L20" s="175">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
@@ -23774,19 +23774,19 @@
       </c>
       <c r="M20" s="118">
         <f t="shared" si="2"/>
-        <v>6514.3552</v>
+        <v>6377.0655999999999</v>
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>767.19462399999998</v>
+        <v>738.00787200000002</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>80.368314880000014</v>
+        <v>77.310824640000007</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>7361.9181388799998</v>
+        <v>7192.3842966399998</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23794,7 +23794,7 @@
       </c>
       <c r="U20" s="164">
         <f>+'7'!P35</f>
-        <v>5757.0168860000013</v>
+        <v>5537.9999392500013</v>
       </c>
     </row>
     <row r="21" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23836,7 +23836,7 @@
       </c>
       <c r="K21" s="172">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
-        <v>30.508800000000004</v>
+        <v>195.76480000000004</v>
       </c>
       <c r="L21" s="175">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
@@ -23844,19 +23844,19 @@
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>8020.9087999999992</v>
+        <v>7855.652799999998</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>1022.33536</v>
+        <v>988.72483199999999</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>114.41134144000002</v>
+        <v>110.23189008</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>9157.6555014399983</v>
+        <v>8954.609522079998</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -23864,7 +23864,7 @@
       </c>
       <c r="U21" s="164">
         <f>+'8'!P35</f>
-        <v>3008.4989184000001</v>
+        <v>2894.0451551999995</v>
       </c>
     </row>
     <row r="22" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23910,23 +23910,23 @@
       </c>
       <c r="L22" s="175">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>105.92100000000002</v>
+        <v>164.76600000000002</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>2425.5909000000006</v>
+        <v>2366.7459000000003</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>292.977486</v>
+        <v>280.97310599999997</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>29.561021130000004</v>
+        <v>28.076950230000001</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>2748.1294071300008</v>
+        <v>2675.7959562300002</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -23934,7 +23934,7 @@
       </c>
       <c r="U22" s="164">
         <f>+'9'!P35</f>
-        <v>2367.1331819999996</v>
+        <v>2277.07920225</v>
       </c>
     </row>
     <row r="23" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -24004,7 +24004,7 @@
       </c>
       <c r="U23" s="164">
         <f>+'10'!P35</f>
-        <v>538.64712270000007</v>
+        <v>509.21285369999998</v>
       </c>
     </row>
     <row r="24" spans="1:21 16384:16384" ht="29.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.65">
@@ -24074,7 +24074,7 @@
       </c>
       <c r="U24" s="164">
         <f>+'11'!P35</f>
-        <v>3277.5516672000003</v>
+        <v>3152.8622015999999</v>
       </c>
     </row>
     <row r="25" spans="1:21 16384:16384" ht="26.5" thickBot="1" x14ac:dyDescent="0.65">
@@ -24107,27 +24107,27 @@
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
-        <v>118.68570000000003</v>
+        <v>750.89717500000006</v>
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>1690.4446</v>
+        <v>1749.2896000000001</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>27850.594699999998</v>
+        <v>27159.538224999997</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>4087.6794739999996</v>
+        <v>3941.8767615000002</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>360.84311455000005</v>
+        <v>347.1022285725</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>32299.117288549998</v>
+        <v>31448.517215072497</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24135,7 +24135,7 @@
       </c>
       <c r="U25" s="164">
         <f>+'12'!P35</f>
-        <v>5014.1648640000003</v>
+        <v>4823.4085919999998</v>
       </c>
     </row>
     <row r="26" spans="1:21 16384:16384" ht="26" x14ac:dyDescent="0.6">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="U26" s="164">
         <f>+'13'!P35</f>
-        <v>1041.9731226000001</v>
+        <v>985.03470059999995</v>
       </c>
     </row>
     <row r="27" spans="1:21 16384:16384" ht="26" x14ac:dyDescent="0.6">
@@ -24367,7 +24367,7 @@
       </c>
       <c r="U34" s="165">
         <f>SUM(U14:U33)</f>
-        <v>33427.286942350001</v>
+        <v>32204.302709272502</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24421,7 +24421,7 @@
       <c r="O37" s="250"/>
       <c r="P37" s="153">
         <f>L25</f>
-        <v>1690.4446</v>
+        <v>1749.2896000000001</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24442,7 +24442,7 @@
       <c r="O38" s="250"/>
       <c r="P38" s="154">
         <f>K25</f>
-        <v>118.68570000000003</v>
+        <v>750.89717500000006</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24464,7 +24464,7 @@
       <c r="O39" s="250"/>
       <c r="P39" s="153">
         <f>P36-P37-P38</f>
-        <v>27850.594699999998</v>
+        <v>27159.538224999997</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24489,7 +24489,7 @@
       </c>
       <c r="P40" s="153">
         <f>N25</f>
-        <v>4087.6794739999996</v>
+        <v>3941.8767615000002</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24511,7 +24511,7 @@
       <c r="O41" s="252"/>
       <c r="P41" s="153">
         <f>P39+P40</f>
-        <v>31938.274173999998</v>
+        <v>31101.414986499996</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24536,7 +24536,7 @@
       </c>
       <c r="P42" s="153">
         <f>O42*P41</f>
-        <v>798.45685434999996</v>
+        <v>777.53537466249998</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24546,7 +24546,7 @@
       <c r="O43" s="230"/>
       <c r="P43" s="160">
         <f>P41+P42</f>
-        <v>32736.731028349997</v>
+        <v>31878.950361162497</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24726,7 +24726,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -24754,7 +24754,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -25177,7 +25177,7 @@
       </c>
       <c r="J17" s="117"/>
       <c r="K17" s="104">
-        <f t="shared" ref="K17:K21" si="4">I17*3.5%</f>
+        <f t="shared" ref="K17:K22" si="4">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -25579,8 +25579,8 @@
         <v>470.76000000000005</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="4"/>
         <v>16.476600000000005</v>
       </c>
       <c r="L22" s="120">
@@ -26232,7 +26232,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -26260,7 +26260,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -26561,7 +26561,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -26620,8 +26620,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -26680,7 +26680,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -26738,9 +26738,9 @@
         <v>508.48</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>17.796800000000001</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
@@ -26748,19 +26748,19 @@
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>467.80160000000001</v>
+        <v>450.00479999999999</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>84.204288000000005</v>
+        <v>81.000863999999993</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>2.7600294400000003</v>
+        <v>2.65502832</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>554.76591744000007</v>
+        <v>533.66069232000007</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26796,9 +26796,9 @@
         <v>435.84000000000003</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>15.254400000000002</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
@@ -26806,19 +26806,19 @@
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>400.97280000000001</v>
+        <v>385.71840000000003</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>72.175104000000005</v>
+        <v>69.429311999999996</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>2.3657395200000004</v>
+        <v>2.2757385600000002</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>475.51364352000002</v>
+        <v>457.42345055999999</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26854,9 +26854,9 @@
         <v>508.48</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>17.796800000000001</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
@@ -26864,19 +26864,19 @@
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>467.80160000000001</v>
+        <v>450.00479999999999</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>84.204288000000005</v>
+        <v>81.000863999999993</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>2.7600294400000003</v>
+        <v>2.65502832</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>554.76591744000007</v>
+        <v>533.66069232000007</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26910,12 +26910,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -27071,7 +27071,7 @@
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>50.847999999999999</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
@@ -27079,19 +27079,19 @@
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1336.576</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>240.58368000000002</v>
+        <v>231.43104</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>7.8857984000000005</v>
+        <v>7.5857951999999997</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1585.0454784000001</v>
+        <v>1524.7448352000001</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27183,7 +27183,7 @@
       <c r="O30" s="250"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>0</v>
+        <v>50.847999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27205,7 +27205,7 @@
       <c r="O31" s="250"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1336.5760000000002</v>
+        <v>1285.7280000000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27230,7 +27230,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>240.58368000000002</v>
+        <v>231.43104</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27252,7 +27252,7 @@
       <c r="O33" s="252"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1577.1596800000002</v>
+        <v>1517.1590400000002</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27277,7 +27277,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>7.8857984000000014</v>
+        <v>7.5857952000000015</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -27287,7 +27287,7 @@
       <c r="O35" s="230"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1585.0454784000003</v>
+        <v>1524.7448352000001</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27459,7 +27459,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -27487,7 +27487,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -27788,7 +27788,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -27847,8 +27847,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -27907,7 +27907,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -27963,7 +27963,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -28019,7 +28019,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -28077,9 +28077,9 @@
         <v>871.68000000000006</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30.508800000000004</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
@@ -28087,19 +28087,19 @@
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>801.94560000000001</v>
+        <v>771.43680000000006</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>144.35020800000001</v>
+        <v>138.85862399999999</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>23.657395200000003</v>
+        <v>22.757385600000003</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>969.95320320000008</v>
+        <v>933.05280960000005</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28135,29 +28135,29 @@
         <v>470.76000000000005</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>16.476600000000005</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>23.538000000000004</v>
+        <f>I22*10%</f>
+        <v>47.076000000000008</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>430.74540000000002</v>
+        <v>407.20740000000001</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>77.534171999999998</v>
+        <v>73.297331999999997</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>12.706989300000002</v>
+        <v>12.0126183</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>520.98656130000006</v>
+        <v>492.51735029999998</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28296,27 +28296,27 @@
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>16.476600000000005</v>
+        <v>46.985400000000013</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>93.272400000000005</v>
+        <v>116.81040000000002</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1232.691</v>
+        <v>1178.6442000000002</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>221.88438000000002</v>
+        <v>212.155956</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>36.364384500000007</v>
+        <v>34.770003900000006</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1490.9397645000001</v>
+        <v>1425.5701598999999</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28387,7 +28387,7 @@
       <c r="O29" s="250"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>93.272400000000005</v>
+        <v>116.81040000000002</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28408,7 +28408,7 @@
       <c r="O30" s="250"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>16.476600000000005</v>
+        <v>46.985400000000013</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28430,7 +28430,7 @@
       <c r="O31" s="250"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1232.691</v>
+        <v>1178.6442</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28455,7 +28455,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>221.88438000000002</v>
+        <v>212.155956</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28477,7 +28477,7 @@
       <c r="O33" s="252"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1454.57538</v>
+        <v>1390.800156</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28502,7 +28502,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>36.3643845</v>
+        <v>34.770003899999999</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28512,7 +28512,7 @@
       <c r="O35" s="230"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1490.9397644999999</v>
+        <v>1425.5701598999999</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -28683,7 +28683,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -28711,7 +28711,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -29012,7 +29012,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -29073,9 +29073,9 @@
         <v>2098.5</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
-        <v>0</v>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
+        <v>73.447500000000005</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
@@ -29083,19 +29083,19 @@
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>1930.62</v>
+        <v>1857.1725000000001</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>424.7364</v>
+        <v>408.57795000000004</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>11.776781999999999</v>
+        <v>11.328752250000001</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>2367.1331819999996</v>
+        <v>2277.07920225</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -29133,7 +29133,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29189,7 +29189,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29245,7 +29245,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29301,7 +29301,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -29357,12 +29357,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -29518,7 +29518,7 @@
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>73.447500000000005</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
@@ -29526,19 +29526,19 @@
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1930.62</v>
+        <v>1857.1725000000001</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>424.7364</v>
+        <v>408.57795000000004</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>11.776781999999999</v>
+        <v>11.328752250000001</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>2367.1331819999996</v>
+        <v>2277.07920225</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -29630,7 +29630,7 @@
       <c r="O30" s="250"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>0</v>
+        <v>73.447500000000005</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29652,7 +29652,7 @@
       <c r="O31" s="250"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1930.62</v>
+        <v>1857.1724999999999</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29677,7 +29677,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>424.7364</v>
+        <v>408.57795000000004</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29699,7 +29699,7 @@
       <c r="O33" s="252"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>2355.3563999999997</v>
+        <v>2265.75045</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29724,7 +29724,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>11.776781999999999</v>
+        <v>11.328752250000001</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29734,7 +29734,7 @@
       <c r="O35" s="230"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>2367.1331819999996</v>
+        <v>2277.07920225</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29906,7 +29906,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -29934,7 +29934,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -30235,7 +30235,7 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
@@ -30294,8 +30294,8 @@
         <v>0</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
@@ -30354,7 +30354,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -30412,9 +30412,9 @@
         <v>581.12</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20.339200000000002</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
@@ -30422,19 +30422,19 @@
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>534.63040000000001</v>
+        <v>514.2912</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>96.233471999999992</v>
+        <v>92.572416000000004</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>15.771596800000001</v>
+        <v>15.171590399999999</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>646.63546880000001</v>
+        <v>622.03520639999999</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30470,9 +30470,9 @@
         <v>290.56</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>10.169600000000001</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
@@ -30480,19 +30480,19 @@
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>267.3152</v>
+        <v>257.1456</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>48.116735999999996</v>
+        <v>46.286208000000002</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>7.8857984000000005</v>
+        <v>7.5857951999999997</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>323.31773440000001</v>
+        <v>311.0176032</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30528,9 +30528,9 @@
         <v>581.12</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20.339200000000002</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
@@ -30538,19 +30538,19 @@
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>534.63040000000001</v>
+        <v>514.2912</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>96.233471999999992</v>
+        <v>92.572416000000004</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>15.771596800000001</v>
+        <v>15.171590399999999</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>646.63546880000001</v>
+        <v>622.03520639999999</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30584,12 +30584,12 @@
         <v>0</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
+        <f>I22*10%</f>
         <v>0</v>
       </c>
       <c r="M22" s="118">
@@ -30745,7 +30745,7 @@
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>50.847999999999999</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
@@ -30753,19 +30753,19 @@
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1336.576</v>
+        <v>1285.7280000000001</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>240.58367999999996</v>
+        <v>231.43104000000002</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>39.428992000000008</v>
+        <v>37.928975999999999</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1616.5886719999999</v>
+        <v>1555.0880160000002</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30857,7 +30857,7 @@
       <c r="O30" s="250"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>0</v>
+        <v>50.847999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30879,7 +30879,7 @@
       <c r="O31" s="250"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1336.5760000000002</v>
+        <v>1285.7280000000003</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30904,7 +30904,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>240.58367999999996</v>
+        <v>231.43104000000002</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30926,7 +30926,7 @@
       <c r="O33" s="252"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1577.1596800000002</v>
+        <v>1517.1590400000002</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30951,7 +30951,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>39.428992000000008</v>
+        <v>37.928976000000006</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30961,7 +30961,7 @@
       <c r="O35" s="230"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1616.5886720000003</v>
+        <v>1555.0880160000002</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -31133,7 +31133,7 @@
       <c r="M4" s="211"/>
       <c r="N4" s="212">
         <f ca="1">TODAY()</f>
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="O4" s="212"/>
       <c r="P4" s="212"/>
@@ -31161,7 +31161,7 @@
       <c r="M5" s="211"/>
       <c r="N5" s="212">
         <f ca="1">N4-1</f>
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="O5" s="210"/>
       <c r="P5" s="210"/>
@@ -31464,8 +31464,8 @@
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
-        <f>I16*$K$13</f>
-        <v>0</v>
+        <f>I16*3.5%</f>
+        <v>11.017125</v>
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
@@ -31473,19 +31473,19 @@
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>289.59299999999996</v>
+        <v>278.57587499999994</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>63.710459999999991</v>
+        <v>61.286692499999987</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>1.7665172999999998</v>
+        <v>1.6993128374999997</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>355.06997729999995</v>
+        <v>341.56188033749993</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -31525,9 +31525,9 @@
         <v>629.54999999999995</v>
       </c>
       <c r="J17" s="117"/>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
-        <v>0</v>
+      <c r="K17" s="104">
+        <f t="shared" ref="K17:K22" si="3">I17*3.5%</f>
+        <v>22.03425</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
@@ -31535,19 +31535,19 @@
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>579.18599999999992</v>
+        <v>557.15174999999988</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>127.42091999999998</v>
+        <v>122.57338499999997</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>3.5330345999999997</v>
+        <v>3.3986256749999995</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>710.1399545999999</v>
+        <v>683.12376067499986</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -31585,7 +31585,7 @@
         <v>0</v>
       </c>
       <c r="J18" s="117"/>
-      <c r="K18" s="1">
+      <c r="K18" s="104">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -31643,9 +31643,9 @@
         <v>217.92000000000002</v>
       </c>
       <c r="J19" s="117"/>
-      <c r="K19" s="1">
+      <c r="K19" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7.6272000000000011</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
@@ -31653,19 +31653,19 @@
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>200.4864</v>
+        <v>192.85920000000002</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>44.107008</v>
+        <v>42.429024000000005</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>1.2229670400000001</v>
+        <v>1.17644112</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>245.81637504</v>
+        <v>236.46466512000001</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31701,9 +31701,9 @@
         <v>871.68000000000006</v>
       </c>
       <c r="J20" s="117"/>
-      <c r="K20" s="1">
+      <c r="K20" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30.508800000000004</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
@@ -31711,19 +31711,19 @@
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>801.94560000000001</v>
+        <v>771.43680000000006</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>176.428032</v>
+        <v>169.71609600000002</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>4.8918681600000005</v>
+        <v>4.70576448</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>983.26550015999999</v>
+        <v>945.85866048000003</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31759,9 +31759,9 @@
         <v>435.84000000000003</v>
       </c>
       <c r="J21" s="117"/>
-      <c r="K21" s="1">
+      <c r="K21" s="104">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>15.254400000000002</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
@@ -31769,19 +31769,19 @@
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>400.97280000000001</v>
+        <v>385.71840000000003</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>88.214016000000001</v>
+        <v>84.858048000000011</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>2.4459340800000002</v>
+        <v>2.35288224</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>491.63275007999999</v>
+        <v>472.92933024000001</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31817,29 +31817,29 @@
         <v>235.38000000000002</v>
       </c>
       <c r="J22" s="117"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="104">
+        <f t="shared" si="3"/>
         <v>8.2383000000000024</v>
       </c>
       <c r="L22" s="120">
-        <f>I22*5%</f>
-        <v>11.769000000000002</v>
+        <f>I22*10%</f>
+        <v>23.538000000000004</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>215.37270000000001</v>
+        <v>203.6037</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>47.381993999999999</v>
+        <v>44.792814</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>1.3137734700000001</v>
+        <v>1.24198257</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>264.06846747000003</v>
+        <v>249.63849657</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31978,27 +31978,27 @@
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>8.2383000000000024</v>
+        <v>94.680075000000016</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>209.3502</v>
+        <v>221.11920000000001</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>2487.5564999999997</v>
+        <v>2389.3457250000001</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>547.26242999999999</v>
+        <v>525.65605949999997</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>15.174094650000001</v>
+        <v>14.575008922499999</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>3049.9930246499998</v>
+        <v>2929.5767934224996</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -32069,7 +32069,7 @@
       <c r="O29" s="250"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>209.3502</v>
+        <v>221.11920000000001</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32090,7 +32090,7 @@
       <c r="O30" s="250"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>8.2383000000000024</v>
+        <v>94.680075000000016</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32112,7 +32112,7 @@
       <c r="O31" s="250"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>2487.5565000000001</v>
+        <v>2389.3457249999997</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32137,7 +32137,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>547.26242999999999</v>
+        <v>525.65605949999997</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -32159,7 +32159,7 @@
       <c r="O33" s="252"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>3034.8189300000004</v>
+        <v>2915.0017844999998</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -32184,7 +32184,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>15.174094650000002</v>
+        <v>14.575008922499999</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -32194,7 +32194,7 @@
       <c r="O35" s="230"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>3049.9930246500003</v>
+        <v>2929.5767934224996</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
